--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -515,7 +515,7 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>347_金边万年青_undefined_undefined_1bunch</v>
+        <v>348_万年青_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -517,6 +517,9 @@
       <c r="C11" t="str">
         <v>348_万年青_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -575,7 +578,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610100</v>
+        <v>0201015555610106</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,9 +521,89 @@
         <v>6</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +658,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106</v>
+        <v>0201015555610106101051015303020200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -600,6 +600,9 @@
       <c r="C21" t="str">
         <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
       </c>
+      <c r="F21" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -658,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106101051015303020200</v>
+        <v>02010155556101061010510153030202030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,9 +604,95 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>4</v>
+      </c>
+      <c r="C28" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>5</v>
+      </c>
+      <c r="C29" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -661,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010155556101061010510153030202030</v>
+        <v>02010155556101061010510153030202030561065100105510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -689,6 +689,9 @@
       <c r="A31" t="str">
         <v>6</v>
       </c>
+      <c r="C31" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -692,6 +692,9 @@
       <c r="C31" t="str">
         <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -750,7 +753,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010155556101061010510153030202030561065100105510100</v>
+        <v>02010155556101061010510153030202030561065100105510108</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -696,9 +696,89 @@
         <v>8</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>7</v>
+      </c>
+      <c r="C36" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -753,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010155556101061010510153030202030561065100105510108</v>
+        <v>02010155556101061010510153030202030561065100105510108953102105620</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -775,6 +775,9 @@
       <c r="C41" t="str">
         <v>48_香格里拉_undefined_Gerbera L._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -833,7 +836,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010155556101061010510153030202030561065100105510108953102105620</v>
+        <v>020101555561010610105101530302020305610651001055101089531021056210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -779,9 +779,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>8</v>
+      </c>
+      <c r="C44" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -836,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101555561010610105101530302020305610651001055101089531021056210</v>
+        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -856,7 +856,7 @@
     </row>
     <row r="51">
       <c r="C51" t="str">
-        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -858,6 +858,9 @@
       <c r="C51" t="str">
         <v>447_黄金球_craspedia_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -916,7 +919,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510100</v>
+        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -859,12 +859,95 @@
         <v>447_黄金球_craspedia_undefined_1bunch</v>
       </c>
       <c r="F51" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>9</v>
+      </c>
+      <c r="C52" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>10</v>
+      </c>
+      <c r="C60" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -919,7 +1002,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101</v>
+        <v>02010155556101061010510153030202030561065100105510108953102105621010105105105101010661051010515150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -944,6 +944,9 @@
       <c r="C61" t="str">
         <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1002,7 +1005,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010155556101061010510153030202030561065100105510108953102105621010105105105101010661051010515150</v>
+        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -948,9 +948,91 @@
         <v>10</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="C64" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>11</v>
+      </c>
+      <c r="C67" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F67" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1005,7 +1087,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510</v>
+        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510515105555550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -1029,6 +1029,9 @@
       <c r="C71" t="str">
         <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
       </c>
+      <c r="F71" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1087,7 +1090,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510515105555550</v>
+        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101066105101051515105151055555510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1033,9 +1033,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="C75" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="C76" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str">
+        <v>12</v>
+      </c>
+      <c r="C78" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F78" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F80" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1090,7 +1173,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101066105101051515105151055555510</v>
+        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510515105555551015151515152055250</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -1115,6 +1115,9 @@
       <c r="C81" t="str">
         <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
       </c>
+      <c r="F81" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1173,7 +1176,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101555561010610105101530302020305610651001055101089531021056210101051051051010106610510105151510515105555551015151515152055250</v>
+        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101066105101051515105151055555510151515151520552515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1119,9 +1119,146 @@
         <v>15</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>13</v>
+      </c>
+      <c r="C82" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F82" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F83" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F84" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F85" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F86" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F88" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F90" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>14</v>
+      </c>
+      <c r="C91" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F91" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>15</v>
+      </c>
+      <c r="C93" t="str">
+        <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
+      </c>
+      <c r="F93" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F94" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="str">
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F95" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F96" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F97" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1176,7 +1313,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101066105101051515105151055555510151515151520552515</v>
+        <v>0201015555610106101051015303020203056106510010551010895310210562101010510510510101066105101051515105151055555510151515151520552515915101051015201045510105105</v>
       </c>
     </row>
   </sheetData>
